--- a/China NEA/review_workbooks/2025-01-27_2024年光伏发电建设情况---国家能源局_review.xlsx
+++ b/China NEA/review_workbooks/2025-01-27_2024年光伏发电建设情况---国家能源局_review.xlsx
@@ -428,1784 +428,1014 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
       <c r="B1" t="n">
-        <v>0</v>
+        <v>27757</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>15939</v>
       </c>
       <c r="D1" t="n">
+        <v>11818</v>
+      </c>
+      <c r="E1" t="n">
+        <v>2955</v>
+      </c>
+      <c r="F1" t="n">
+        <v>88568</v>
+      </c>
+      <c r="G1" t="n">
+        <v>51089</v>
+      </c>
+      <c r="H1" t="n">
+        <v>37478</v>
+      </c>
+      <c r="I1" t="n">
+        <v>14515</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>724.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1786.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7202.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4294.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2908.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1888.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>986.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>677</v>
+      </c>
+      <c r="D5" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3476.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2500.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>975.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>597.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1920.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>999.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>921.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7613.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2592.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5020.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2764.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2455.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2321.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>134</v>
+      </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4810.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4502.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>133.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>256.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1213.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>542.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>359.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>583</v>
+      </c>
+      <c r="G9" t="n">
+        <v>382</v>
+      </c>
+      <c r="H9" t="n">
+        <v>201</v>
+      </c>
+      <c r="I9" t="n">
+        <v>107.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>717.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>471.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>245.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>122</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>122</v>
+      </c>
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="E1" t="n">
+      <c r="F11" t="n">
+        <v>411.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2236.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>439.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1797.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>841.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6164.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1595</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4569.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1701.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1370.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E13" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4727.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>833.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3893.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>444.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1088.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>156</v>
+      </c>
+      <c r="D14" t="n">
+        <v>932.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4311.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1441.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2869.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1349.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1258.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1181.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>394.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>570.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2563.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1374.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1189.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>648.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>617.7</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>617.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4349.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>630</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3719.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2317.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1022.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>624</v>
+      </c>
+      <c r="E18" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2147.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1362.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>317.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>534.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1873.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>486.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1387.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>346.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>508.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1082.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>889.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>193</v>
+      </c>
+      <c r="I21" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1141.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>704.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>437.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3433</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2523.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>909.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>435.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>620</v>
+      </c>
+      <c r="C23" t="n">
+        <v>540.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>80</v>
+      </c>
+      <c r="E23" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3138.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2954.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1083.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3642</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3604.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>437.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2624</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2449.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2668.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2659.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5345.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5318.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>新疆兵团</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>403.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>398.4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1594.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>478.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1115.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4115.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1373.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2742.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>342.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>919.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>281.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>638.1</v>
+      </c>
+      <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="F1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省（区、
-市）</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2024年新增并网容量</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2024年新增并网容量</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2024年新增并网容量</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2024年新增并网容量</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>截至2024年底累计并网容量</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>截至2024年底累计并网容量</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>截至2024年底累计并网容量</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>截至2024年底累计并网容量</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>省（区、
-市）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>其中：集中
-式光伏电站</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>其中：集
-中式光伏
-电站</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>其中：
-户用光伏</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>其中：
-户用光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>27757</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>15939</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>11818</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2955</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>88568</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>51089</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>37478</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14515</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>130.3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>122.2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>234.6</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>182.2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>724.1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>351.3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>372.9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1786.3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1270.5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>515.7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>157.3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7202.4</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4294.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2908.3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1888.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>986.5</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>309.5</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3476.8</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2500.9</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>975.9</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>597.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1920.9</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>999.1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>921.8</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>205.7</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>7613.4</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2592.9</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5020.6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2764.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2455.3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2321.3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4810.9</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4502.7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>308.1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>133.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>256.3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>235.5</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>141.7</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1213.9</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>542.1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>671.8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>359.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>123.2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>81.4</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>583.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>382.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>201.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>107.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>152.2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>717.1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>471.1</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>245.9</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>122.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>122.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>411.4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>39.8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>371.6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2236.7</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>439.2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1797.4</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>841.8</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6164.7</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1595.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4569.7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1701.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1370.8</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>166.8</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1204.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>207.2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4727.5</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>833.9</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3893.6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>444.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1088.2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>932.2</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>418.8</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4311.3</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1441.9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2869.3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1349.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>383.8</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>351.4</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1258.3</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1181.8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>394.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>570.7</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>393.4</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>177.3</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2563.9</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1374.5</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1189.4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>648.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>617.7</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>617.7</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>86.6</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4349.1</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>630.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3719.1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2317.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1022.7</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>398.7</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>37.3</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>3510.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2147.8</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1362.1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>317.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>621.6</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>534.8</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1873.4</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>486.1</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1387.3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>346.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>152.9</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>122.5</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>309.8</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>107.2</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>202.6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>508.8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>366.5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>142.3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1082.3</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>889.3</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>23.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1141.5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>704.4</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>437.1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>183.7</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>3433.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2523.9</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>909.1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>435.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>620.0</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>540.1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>3138.8</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2954.9</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>183.9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1102.0</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1083.5</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>3642.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3604.3</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>37.8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>487.4</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>437.7</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2624.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2449.3</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>174.7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2668.2</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2659.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>5345.6</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>5318.7</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2052.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1088.6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>963.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>21.6</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>新疆兵团</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>102.8</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>102.8</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>329.2</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>329.2</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>268.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>740.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25.5</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>159.4</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>149.6</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>403.9</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>398.4</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1985.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1876</v>
+      </c>
+      <c r="H32" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1594.2</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>478.3</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1115.9</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>119.1</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>4115.5</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1373.3</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2742.3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>342.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>919.8</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>281.6</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>638.1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2052.3</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>1088.6</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>963.7</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>268.3</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>159.8</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>108.5</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>740.8</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>472.5</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>268.4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>408.8</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>315.5</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>93.3</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1985.6</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>1876.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>109.6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>云南</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1651.3</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1495.3</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3723.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3433.1</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>289.9</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1651.3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1495.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>156</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3723</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3433.1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>34.8</v>
       </c>
     </row>
   </sheetData>
@@ -2253,11 +1483,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0省（区、市）</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>省(区、市)</t>
@@ -2278,11 +1504,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>12024年新增并网容量</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>2024年新增并网容量</t>
@@ -2303,11 +1525,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>22024年新增并网容量其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2024年新增并网容量_其中：集中式光伏电站</t>
@@ -2328,11 +1546,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>32024年新增并网容量其中：分布式光伏</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2024年新增并网容量_其中：分布式光伏</t>
@@ -2353,11 +1567,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>42024年新增并网容量其中：分布式光伏其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2024年新增并网容量_其中：户用光伏</t>
@@ -2378,11 +1588,7 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5截至2024年底累计并网容量</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>截至2024年底累计并网容量</t>
@@ -2403,11 +1609,7 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6截至2024年底累计并网容量其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>截至2024年底累计并网容量_其中：集中式光伏电站</t>
@@ -2428,11 +1630,7 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7截至2024年底累计并网容量其中：分布式光伏</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>截至2024年底累计并网容量_其中：分布式光伏</t>
@@ -2453,11 +1651,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>8截至2024年底累计并网容量其中：分布式光伏其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>截至2024年底累计并网容量_其中：户用光伏</t>
@@ -3573,9 +2767,7 @@
         <v>102.8</v>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>329.2</v>
       </c>
@@ -3583,9 +2775,7 @@
         <v>329.2</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="b">
         <v>0</v>
       </c>
@@ -5033,9 +4223,7 @@
         <v>102.8</v>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>329.2</v>
       </c>
@@ -5043,9 +4231,7 @@
         <v>329.2</v>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="b">
         <v>0</v>
       </c>
